--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105386</v>
+        <v>120105384</v>
       </c>
       <c r="B3" t="n">
-        <v>94574</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105384</v>
+        <v>120105388</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +922,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>94574</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R5" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105387</v>
+        <v>120105384</v>
       </c>
       <c r="B2" t="n">
-        <v>94574</v>
+        <v>91863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R2" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105384</v>
+        <v>120105388</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>94574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R4" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105386</v>
+        <v>120105387</v>
       </c>
       <c r="B5" t="n">
         <v>94574</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>94574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R3" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105386</v>
+        <v>120105388</v>
       </c>
       <c r="B4" t="n">
-        <v>94574</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105384</v>
+        <v>120105388</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R2" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105386</v>
+        <v>120105384</v>
       </c>
       <c r="B3" t="n">
-        <v>94574</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R4" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
         <v>120105387</v>
       </c>
       <c r="B5" t="n">
-        <v>94574</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>94597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R2" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105384</v>
+        <v>120105388</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105386</v>
+        <v>120105387</v>
       </c>
       <c r="B4" t="n">
         <v>94597</v>
@@ -954,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105387</v>
+        <v>120105384</v>
       </c>
       <c r="B5" t="n">
-        <v>94597</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R5" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105386</v>
+        <v>120105384</v>
       </c>
       <c r="B2" t="n">
-        <v>94597</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105388</v>
+        <v>120105387</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>94597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105387</v>
+        <v>120105388</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105384</v>
+        <v>120105386</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105388</v>
+        <v>120105386</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R4" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105386</v>
+        <v>120105388</v>
       </c>
       <c r="B5" t="n">
-        <v>94597</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105384</v>
+        <v>120105387</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R2" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105387</v>
+        <v>120105386</v>
       </c>
       <c r="B3" t="n">
         <v>94597</v>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R3" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120105386</v>
+        <v>120105388</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R4" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105388</v>
+        <v>120105384</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R5" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120105387</v>
+        <v>120105386</v>
       </c>
       <c r="B2" t="n">
         <v>94597</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R2" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105386</v>
+        <v>120105384</v>
       </c>
       <c r="B3" t="n">
-        <v>94597</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105384</v>
+        <v>120105387</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R5" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37405-2024 artfynd.xlsx
+++ b/artfynd/A 37405-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120105384</v>
+        <v>120105387</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581503</v>
+        <v>581461</v>
       </c>
       <c r="R3" t="n">
-        <v>6508896</v>
+        <v>6508917</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120105387</v>
+        <v>120105384</v>
       </c>
       <c r="B5" t="n">
-        <v>94597</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581461</v>
+        <v>581503</v>
       </c>
       <c r="R5" t="n">
-        <v>6508917</v>
+        <v>6508896</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
